--- a/intake_forms/038_medical_tour_service_agreement--intake_forms.xlsx
+++ b/intake_forms/038_medical_tour_service_agreement--intake_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,20 +571,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Question 1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Medical Tour Service Agreement Introduction</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please read and understand the agreement before signing.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +598,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Question 2</t>
+          <t>What is your medical history?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,20 +621,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Question 3</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>When is your appointment scheduled?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Format - YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,7 +684,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,20 +694,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Question 1</t>
+          <t>Can you please provide your email address?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,13 +717,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Question 2</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is your favorite time of day?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Format - 24-hour format</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,13 +744,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Question 3</t>
+          <t>Select the correct options for the following questions</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,13 +767,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Question 4</t>
+          <t>How many hours do you work?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,13 +790,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Question 5</t>
+          <t>Medical Tour Service Agreement Second Page Section1 Question5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -801,20 +813,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Question 6</t>
+          <t>What is your favorite color?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,20 +836,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Question 7</t>
+          <t>Medical Tour Service Agreement Second Page Section1 Question7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -847,20 +859,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Question 8</t>
+          <t>Can you please provide a brief description of your favorite food?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -870,20 +882,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Question 9</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Can you please provide a photo of your medical ID?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please upload a photo of your medical ID</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,13 +909,13 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Question 10</t>
+          <t>How many pets do you have?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -916,174 +932,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Question 11</t>
+          <t>Medical Tour Service Agreement Second Page Section1 Question11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question12</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Question 12</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question13</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Question 13</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question14</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Question 14</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question15</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Question 15</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question16</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Question 16</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question17</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Question 17</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question18</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Question 18</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,7 +953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1279,7 +1134,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>medical_tour_service_agreement_second_page_section1_question8_choices</t>
+          <t>medical_tour_service_agreement_second_page_section1_question11_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1151,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>medical_tour_service_agreement_second_page_section1_question8_choices</t>
+          <t>medical_tour_service_agreement_second_page_section1_question11_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1168,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>medical_tour_service_agreement_second_page_section1_question8_choices</t>
+          <t>medical_tour_service_agreement_second_page_section1_question11_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1322,516 +1177,6 @@
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question9_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option_a</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question9_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option_b</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question9_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option_c</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question10_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option_a</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question10_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option_b</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question10_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option_c</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question11_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option_a</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question11_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option_b</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question11_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option_c</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question12_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option_a</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question12_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option_b</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question12_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option_c</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question13_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option_a</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question13_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option_b</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question13_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option_c</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question14_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option_a</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question14_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option_b</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question14_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option_c</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question15_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>option_a</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question15_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option_b</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question15_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>option_c</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question16_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>option_a</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question16_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>option_b</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question16_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>option_c</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question17_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>option_a</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question17_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>option_b</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question17_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>option_c</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question18_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>option_a</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question18_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>option_b</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>medical_tour_service_agreement_second_page_section1_question18_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>option_c</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
         <is>
           <t>Option C</t>
         </is>
